--- a/ProductionBuild/media.result.xlsx
+++ b/ProductionBuild/media.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -392,1009 +392,882 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>America Movil SAB de CV</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGRPY</t>
+          <t>AMX</t>
         </is>
       </c>
       <c r="C2">
-        <v>1.1849</v>
+        <v>0.4173</v>
       </c>
       <c r="D2">
-        <v>11.849</v>
+        <v>4.173</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="F2">
-        <v>30.45000076293945</v>
+        <v>25.72999954223633</v>
       </c>
       <c r="G2">
-        <v>5.450000762939453</v>
+        <v>13.15999984741211</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BCE Inc.</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALIZY</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="C3">
-        <v>1.1421</v>
+        <v>2.161181818181818</v>
       </c>
       <c r="D3">
-        <v>11.421</v>
+        <v>23.773</v>
       </c>
       <c r="E3">
-        <v>16.47999954223633</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="F3">
-        <v>45.83000183105469</v>
+        <v>23.72999954223633</v>
       </c>
       <c r="G3">
-        <v>29.35000228881836</v>
+        <v>-19.51000213623047</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bezeq The Israel Telecommunication Corp Ltd</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANZGY</t>
+          <t>BZQIY</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.9964000000000001</v>
+        <v>0.4091428571428571</v>
       </c>
       <c r="D4">
-        <v>9.964</v>
+        <v>2.864</v>
       </c>
       <c r="E4">
+        <v>9.510000228881836</v>
+      </c>
+      <c r="F4">
+        <v>13.85000038146973</v>
+      </c>
+      <c r="G4">
+        <v>4.340000152587891</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chunghwa Telecom Co Ltd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CHT</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1.5573</v>
+      </c>
+      <c r="D5">
+        <v>15.573</v>
+      </c>
+      <c r="E5">
+        <v>31.54999923706055</v>
+      </c>
+      <c r="F5">
+        <v>43.15000152587891</v>
+      </c>
+      <c r="G5">
+        <v>11.60000228881836</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Comcast Corp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.8297450909090909</v>
+      </c>
+      <c r="D6">
+        <v>9.127196</v>
+      </c>
+      <c r="E6">
+        <v>32.35707473754883</v>
+      </c>
+      <c r="F6">
+        <v>29.3700008392334</v>
+      </c>
+      <c r="G6">
+        <v>-2.98707389831543</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAR Group Limited</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSXXY</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.6796363636363636</v>
+      </c>
+      <c r="D7">
+        <v>7.476</v>
+      </c>
+      <c r="E7">
+        <v>15.80000019073486</v>
+      </c>
+      <c r="F7">
+        <v>36.77999877929688</v>
+      </c>
+      <c r="G7">
+        <v>20.97999858856201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Deutsche Telekom AG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DTEGY</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.7890909090909091</v>
+      </c>
+      <c r="D8">
+        <v>8.68</v>
+      </c>
+      <c r="E8">
+        <v>17.10000038146973</v>
+      </c>
+      <c r="F8">
+        <v>32.34000015258789</v>
+      </c>
+      <c r="G8">
+        <v>15.23999977111816</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Elisa Corp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ELMUY</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1.0164943</v>
+      </c>
+      <c r="D9">
+        <v>10.164943</v>
+      </c>
+      <c r="E9">
+        <v>18.5</v>
+      </c>
+      <c r="F9">
+        <v>32.75</v>
+      </c>
+      <c r="G9">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Informa Plc</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IFJPY</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.61175</v>
+      </c>
+      <c r="D10">
+        <v>4.894</v>
+      </c>
+      <c r="E10">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="F10">
+        <v>22.36000061035156</v>
+      </c>
+      <c r="G10">
+        <v>5.560001373291016</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KDDI Corp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KDDIY</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.2455</v>
+      </c>
+      <c r="D11">
+        <v>0.491</v>
+      </c>
+      <c r="E11">
+        <v>12.64999961853027</v>
+      </c>
+      <c r="F11">
+        <v>16.35000038146973</v>
+      </c>
+      <c r="G11">
+        <v>3.700000762939453</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KT Corporation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.6457499999999999</v>
+      </c>
+      <c r="D12">
+        <v>2.583</v>
+      </c>
+      <c r="E12">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="F12">
         <v>21.84000015258789</v>
       </c>
-      <c r="F4">
-        <v>26.39999961853027</v>
-      </c>
-      <c r="G4">
-        <v>4.559999465942383</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1.564545454545454</v>
-      </c>
-      <c r="D5">
-        <v>17.21</v>
-      </c>
-      <c r="E5">
-        <v>16.48999977111816</v>
-      </c>
-      <c r="F5">
-        <v>18.95999908447266</v>
-      </c>
-      <c r="G5">
-        <v>2.469999313354492</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AUB</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.9781818181818183</v>
-      </c>
-      <c r="D6">
-        <v>10.76</v>
-      </c>
-      <c r="E6">
-        <v>35.7400016784668</v>
-      </c>
-      <c r="F6">
-        <v>37.56000137329102</v>
-      </c>
-      <c r="G6">
-        <v>1.819999694824219</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AVVIY</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.9795454545454545</v>
-      </c>
-      <c r="D7">
-        <v>10.775</v>
-      </c>
-      <c r="E7">
-        <v>15.53947353363037</v>
-      </c>
-      <c r="F7">
-        <v>17.19000053405762</v>
-      </c>
-      <c r="G7">
-        <v>1.650527000427246</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>AXAHY</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>1.6056</v>
-      </c>
-      <c r="D8">
-        <v>16.056</v>
-      </c>
-      <c r="E8">
-        <v>25.20000076293945</v>
-      </c>
-      <c r="F8">
-        <v>49.31000137329102</v>
-      </c>
-      <c r="G8">
-        <v>24.11000061035156</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BBVA</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.4082727272727272</v>
-      </c>
-      <c r="D9">
-        <v>4.491</v>
-      </c>
-      <c r="E9">
-        <v>6.769999980926514</v>
-      </c>
-      <c r="F9">
-        <v>22.46999931335449</v>
-      </c>
-      <c r="G9">
-        <v>15.69999933242798</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>BCH</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>1.3828666</v>
-      </c>
-      <c r="D10">
-        <v>13.828666</v>
-      </c>
-      <c r="E10">
-        <v>23.48333358764648</v>
-      </c>
-      <c r="F10">
-        <v>39.20000076293945</v>
-      </c>
-      <c r="G10">
-        <v>15.71666717529297</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>1.26</v>
-      </c>
-      <c r="D11">
-        <v>13.86</v>
-      </c>
-      <c r="E11">
-        <v>39.58000183105469</v>
-      </c>
-      <c r="F11">
-        <v>27.23999977111816</v>
-      </c>
-      <c r="G11">
-        <v>-12.34000205993652</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BNPQY</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.915888888888889</v>
-      </c>
-      <c r="D12">
-        <v>17.243</v>
-      </c>
-      <c r="E12">
-        <v>31.85000038146973</v>
-      </c>
-      <c r="F12">
-        <v>53.41999816894531</v>
-      </c>
       <c r="G12">
-        <v>21.56999778747559</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Match Group Inc</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="C13">
-        <v>2.5806</v>
+        <v>1.05</v>
       </c>
       <c r="D13">
-        <v>25.806</v>
+        <v>3.15</v>
       </c>
       <c r="E13">
-        <v>55.68000030517578</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="F13">
-        <v>75.87000274658203</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="G13">
-        <v>20.19000244140625</v>
+        <v>19.42999839782715</v>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NetEase Inc</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BSAC</t>
+          <t>NTES</t>
         </is>
       </c>
       <c r="C14">
-        <v>1.117222222222222</v>
+        <v>1.377272727272727</v>
       </c>
       <c r="D14">
-        <v>10.055</v>
+        <v>15.15</v>
       </c>
       <c r="E14">
-        <v>21.8700008392334</v>
+        <v>43.06800079345703</v>
       </c>
       <c r="F14">
-        <v>34.15999984741211</v>
+        <v>113.2699966430664</v>
       </c>
       <c r="G14">
-        <v>12.28999900817871</v>
+        <v>70.20199584960938</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NTT Inc</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BXSL</t>
+          <t>NTTYY</t>
         </is>
       </c>
       <c r="C15">
-        <v>2.218333333333333</v>
+        <v>0.439</v>
       </c>
       <c r="D15">
-        <v>13.31</v>
+        <v>0.878</v>
+      </c>
+      <c r="E15">
+        <v>21.03499984741211</v>
       </c>
       <c r="F15">
-        <v>24.17000007629395</v>
+        <v>23.73999977111816</v>
+      </c>
+      <c r="G15">
+        <v>2.704999923706055</v>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group Inc.</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CIB</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C16">
-        <v>2.433545454545455</v>
+        <v>3.210909090909091</v>
       </c>
       <c r="D16">
-        <v>26.769</v>
+        <v>35.32</v>
       </c>
       <c r="E16">
-        <v>36.68000030517578</v>
+        <v>63.29999923706055</v>
       </c>
       <c r="F16">
-        <v>73.20999908447266</v>
+        <v>210.1999969482422</v>
       </c>
       <c r="G16">
-        <v>36.52999877929688</v>
+        <v>146.8999977111816</v>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Omnicom Group Inc</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C17">
-        <v>2.987272727272727</v>
+        <v>2.4</v>
       </c>
       <c r="D17">
-        <v>32.86</v>
+        <v>26.4</v>
       </c>
       <c r="E17">
-        <v>41.5</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="F17">
-        <v>48.16999816894531</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="G17">
-        <v>6.669998168945313</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Orange SA</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>ORANY</t>
         </is>
       </c>
       <c r="C18">
-        <v>1.171818181818182</v>
+        <v>0.7399</v>
       </c>
       <c r="D18">
-        <v>12.89</v>
+        <v>7.399</v>
       </c>
       <c r="E18">
-        <v>44.68000030517578</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="F18">
-        <v>29.09000015258789</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="G18">
-        <v>-15.59000015258789</v>
+        <v>5.310000419616699</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PLDT Inc</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DBSDY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19">
-        <v>3.441421636363637</v>
+        <v>1.372727272727273</v>
       </c>
       <c r="D19">
-        <v>37.855638</v>
+        <v>15.1</v>
       </c>
       <c r="E19">
-        <v>43.40909194946289</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="F19">
-        <v>179.1499938964844</v>
+        <v>20.94000053405762</v>
       </c>
       <c r="G19">
-        <v>135.7409019470215</v>
+        <v>-6.60999870300293</v>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Publicis Groupe SA</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DNKEY</t>
+          <t>PUBGY</t>
         </is>
       </c>
       <c r="C20">
-        <v>0.7968000000000001</v>
+        <v>0.6485</v>
       </c>
       <c r="D20">
-        <v>7.968</v>
+        <v>6.485</v>
       </c>
       <c r="E20">
-        <v>15.18000030517578</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="F20">
-        <v>25.79999923706055</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="G20">
-        <v>10.61999893188477</v>
+        <v>5.659999847412109</v>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rogers Communications Inc</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="C21">
-        <v>1.269100090909091</v>
+        <v>1.326</v>
       </c>
       <c r="D21">
-        <v>13.960101</v>
+        <v>14.586</v>
       </c>
       <c r="E21">
-        <v>22.73556709289551</v>
+        <v>38.58000183105469</v>
       </c>
       <c r="F21">
-        <v>50.68000030517578</v>
+        <v>37.47999954223633</v>
       </c>
       <c r="G21">
-        <v>27.94443321228027</v>
+        <v>-1.100002288818359</v>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Swisscom AG</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>SCMWY</t>
         </is>
       </c>
       <c r="C22">
-        <v>0.4990909090909091</v>
+        <v>2.4541</v>
       </c>
       <c r="D22">
-        <v>5.49</v>
+        <v>24.541</v>
       </c>
       <c r="E22">
-        <v>13.22000026702881</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="F22">
-        <v>16.96999931335449</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="G22">
-        <v>3.749999046325684</v>
+        <v>38.59000015258789</v>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Singapore Telecommunications Ltd</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>SGAPY</t>
         </is>
       </c>
       <c r="C23">
-        <v>2.268181818181818</v>
+        <v>1.0242</v>
       </c>
       <c r="D23">
-        <v>24.95</v>
+        <v>10.242</v>
       </c>
       <c r="E23">
-        <v>40.18000030517578</v>
+        <v>24.94000053405762</v>
       </c>
       <c r="F23">
-        <v>90.63999938964844</v>
+        <v>37.47999954223633</v>
       </c>
       <c r="G23">
-        <v>50.45999908447266</v>
+        <v>12.53999900817871</v>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sirius XM Holdings Inc</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="C24">
-        <v>0.8558</v>
+        <v>0.8618181818181818</v>
       </c>
       <c r="D24">
-        <v>8.558</v>
+        <v>9.48</v>
       </c>
       <c r="E24">
-        <v>14.10000038146973</v>
+        <v>44.5</v>
       </c>
       <c r="F24">
-        <v>28.48999977111816</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="G24">
-        <v>14.38999938964844</v>
+        <v>-16.44000053405762</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SK Telecom Co Ltd</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ISNPY</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="C25">
-        <v>1.340444444444444</v>
+        <v>4.299850666666666</v>
       </c>
       <c r="D25">
-        <v>12.064</v>
+        <v>25.799104</v>
       </c>
       <c r="E25">
-        <v>15.22999954223633</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="F25">
-        <v>40.72999954223633</v>
+        <v>38.81999969482422</v>
       </c>
       <c r="G25">
-        <v>25.5</v>
+        <v>4.388370513916016</v>
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AT&amp;T Inc</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JEF</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C26">
-        <v>0.7636609090909091</v>
+        <v>1.487818181818182</v>
       </c>
       <c r="D26">
-        <v>8.400269999999999</v>
+        <v>16.366</v>
       </c>
       <c r="E26">
-        <v>20.81229782104492</v>
+        <v>32.12235641479492</v>
       </c>
       <c r="F26">
-        <v>47.61999893188477</v>
+        <v>25.97999954223633</v>
       </c>
       <c r="G26">
-        <v>26.80770111083984</v>
+        <v>-6.142356872558594</v>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Telenor ASA</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>TELNY</t>
         </is>
       </c>
       <c r="C27">
-        <v>0.6231818181818182</v>
+        <v>1.0068</v>
       </c>
       <c r="D27">
-        <v>6.855</v>
+        <v>10.068</v>
       </c>
       <c r="E27">
-        <v>18.27000045776367</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="F27">
-        <v>22.10000038146973</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G27">
-        <v>3.829999923706055</v>
+        <v>2.530000686645508</v>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Millicom International Cellular SA</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAZ</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="C28">
-        <v>1.957272727272727</v>
+        <v>3.296666666666667</v>
       </c>
       <c r="D28">
-        <v>21.53</v>
-      </c>
-      <c r="E28">
-        <v>41.09000015258789</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F28">
-        <v>48.72000122070313</v>
-      </c>
-      <c r="G28">
-        <v>7.630001068115234</v>
+        <v>83.15000152587891</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Telstra Group Limited</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LNC</t>
+          <t>TLGPY</t>
         </is>
       </c>
       <c r="C29">
-        <v>1.44</v>
+        <v>0.6161818181818182</v>
       </c>
       <c r="D29">
-        <v>15.84</v>
+        <v>6.778</v>
       </c>
       <c r="E29">
-        <v>66.26999664306641</v>
+        <v>18.26000022888184</v>
       </c>
       <c r="F29">
-        <v>36.68999862670898</v>
+        <v>19.14999961853027</v>
       </c>
       <c r="G29">
-        <v>-29.57999801635742</v>
+        <v>0.8899993896484375</v>
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAIN</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="C30">
-        <v>2.883181818181818</v>
+        <v>1.09075</v>
       </c>
       <c r="D30">
-        <v>31.715</v>
+        <v>10.9075</v>
       </c>
       <c r="E30">
-        <v>36.77000045776367</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="F30">
-        <v>54.04999923706055</v>
+        <v>17.68000030517578</v>
       </c>
       <c r="G30">
-        <v>17.27999877929688</v>
+        <v>-11.47999954223633</v>
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Telefonica Brasil SA</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>VIV</t>
         </is>
       </c>
       <c r="C31">
-        <v>3.109363636363637</v>
+        <v>0.6134545454545455</v>
       </c>
       <c r="D31">
-        <v>34.203</v>
+        <v>6.748</v>
       </c>
       <c r="E31">
-        <v>33.90000152587891</v>
+        <v>13.38000011444092</v>
       </c>
       <c r="F31">
-        <v>68.73999786376953</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="G31">
-        <v>34.83999633789063</v>
+        <v>2.489999771118164</v>
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Vodafone Group Public Limited Company</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MFC</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="C32">
-        <v>0.7749090909090909</v>
+        <v>1.1265</v>
       </c>
       <c r="D32">
-        <v>8.523999999999999</v>
+        <v>11.265</v>
       </c>
       <c r="E32">
-        <v>17.81999969482422</v>
+        <v>24.43000030517578</v>
       </c>
       <c r="F32">
-        <v>38.22999954223633</v>
+        <v>15.3100004196167</v>
       </c>
       <c r="G32">
-        <v>20.40999984741211</v>
+        <v>-9.119999885559082</v>
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Verizon Communications Inc</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NLY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C33">
-        <v>3.343636363636364</v>
+        <v>2.295727272727273</v>
       </c>
       <c r="D33">
-        <v>36.78</v>
+        <v>25.253</v>
       </c>
       <c r="E33">
-        <v>39.88000106811523</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="F33">
-        <v>22.60000038146973</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="G33">
-        <v>-17.28000068664551</v>
+        <v>-7.400001525878906</v>
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Warner Music Group Corp</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NWG</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="C34">
-        <v>0.4551158888888889</v>
+        <v>0.5271428571428571</v>
       </c>
       <c r="D34">
-        <v>4.096043</v>
-      </c>
-      <c r="E34">
-        <v>5.959052085876465</v>
+        <v>3.69</v>
       </c>
       <c r="F34">
-        <v>16.11000061035156</v>
-      </c>
-      <c r="G34">
-        <v>10.1509485244751</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>OMF</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>4.45375</v>
-      </c>
-      <c r="D35">
-        <v>35.63</v>
-      </c>
-      <c r="E35">
-        <v>22.13999938964844</v>
-      </c>
-      <c r="F35">
-        <v>58.90999984741211</v>
-      </c>
-      <c r="G35">
-        <v>36.77000045776367</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>OZK</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>1.082818181818182</v>
-      </c>
-      <c r="D36">
-        <v>11.911</v>
-      </c>
-      <c r="E36">
-        <v>52.59000015258789</v>
-      </c>
-      <c r="F36">
-        <v>48.52000045776367</v>
-      </c>
-      <c r="G36">
-        <v>-4.069999694824219</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>PRU</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>3.954545454545455</v>
-      </c>
-      <c r="D37">
-        <v>43.5</v>
-      </c>
-      <c r="E37">
-        <v>104.0599975585938</v>
-      </c>
-      <c r="F37">
-        <v>96.44999694824219</v>
-      </c>
-      <c r="G37">
-        <v>-7.610000610351563</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>0.6113636363636363</v>
-      </c>
-      <c r="D38">
-        <v>6.725000000000001</v>
-      </c>
-      <c r="E38">
-        <v>14.35999965667725</v>
-      </c>
-      <c r="F38">
-        <v>28.35000038146973</v>
-      </c>
-      <c r="G38">
-        <v>13.99000072479248</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>1.554090909090909</v>
-      </c>
-      <c r="D39">
-        <v>17.095</v>
-      </c>
-      <c r="E39">
-        <v>38.40999984741211</v>
-      </c>
-      <c r="F39">
-        <v>70.31999969482422</v>
-      </c>
-      <c r="G39">
-        <v>31.90999984741211</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SSREY</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>1.5439</v>
-      </c>
-      <c r="D40">
-        <v>15.439</v>
-      </c>
-      <c r="E40">
-        <v>23.76000022888184</v>
-      </c>
-      <c r="F40">
-        <v>42.16999816894531</v>
-      </c>
-      <c r="G40">
-        <v>18.40999794006348</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>STWD</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>1.745454545454545</v>
-      </c>
-      <c r="D41">
-        <v>19.2</v>
-      </c>
-      <c r="E41">
-        <v>21.95000076293945</v>
-      </c>
-      <c r="F41">
-        <v>18.23999977111816</v>
-      </c>
-      <c r="G41">
-        <v>-3.710000991821289</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SWDBY</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>1.6139</v>
-      </c>
-      <c r="D42">
-        <v>16.139</v>
-      </c>
-      <c r="E42">
-        <v>24.14999961853027</v>
-      </c>
-      <c r="F42">
-        <v>35.5099983215332</v>
-      </c>
-      <c r="G42">
-        <v>11.35999870300293</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>TFC</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>1.620909090909091</v>
-      </c>
-      <c r="D43">
-        <v>17.83</v>
-      </c>
-      <c r="E43">
-        <v>47.02000045776367</v>
-      </c>
-      <c r="F43">
-        <v>51.06999969482422</v>
-      </c>
-      <c r="G43">
-        <v>4.049999237060547</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>3.789090909090909</v>
-      </c>
-      <c r="D44">
-        <v>41.68</v>
-      </c>
-      <c r="E44">
-        <v>75.26000213623047</v>
-      </c>
-      <c r="F44">
-        <v>99.13999938964844</v>
-      </c>
-      <c r="G44">
-        <v>23.87999725341797</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>UOVEY</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>1.8141</v>
-      </c>
-      <c r="D45">
-        <v>18.141</v>
-      </c>
-      <c r="E45">
-        <v>28.13999938964844</v>
-      </c>
-      <c r="F45">
-        <v>57.18000030517578</v>
-      </c>
-      <c r="G45">
-        <v>29.04000091552734</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>USB</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>1.516818181818182</v>
-      </c>
-      <c r="D46">
-        <v>16.685</v>
-      </c>
-      <c r="E46">
-        <v>51.36999893188477</v>
-      </c>
-      <c r="F46">
-        <v>56.84000015258789</v>
-      </c>
-      <c r="G46">
-        <v>5.470001220703125</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>WF</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>2.34775</v>
-      </c>
-      <c r="D47">
-        <v>9.391</v>
-      </c>
-      <c r="E47">
-        <v>32</v>
-      </c>
-      <c r="F47">
-        <v>71.59999847412109</v>
-      </c>
-      <c r="G47">
-        <v>39.59999847412109</v>
+        <v>29.30999946594238</v>
       </c>
     </row>
   </sheetData>

--- a/ProductionBuild/media.result.xlsx
+++ b/ProductionBuild/media.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,880 +394,400 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>America Movil SAB de CV</t>
+          <t>BCE Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AMX</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="C2">
-        <v>0.4173</v>
+        <v>2.161181818181818</v>
       </c>
       <c r="D2">
-        <v>4.173</v>
+        <v>23.773</v>
       </c>
       <c r="E2">
-        <v>12.56999969482422</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="F2">
-        <v>25.72999954223633</v>
+        <v>23.72999954223633</v>
       </c>
       <c r="G2">
-        <v>13.15999984741211</v>
+        <v>-19.51000213623047</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCE Inc.</t>
+          <t>Comcast Corp</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C3">
-        <v>2.161181818181818</v>
+        <v>0.8297450909090909</v>
       </c>
       <c r="D3">
-        <v>23.773</v>
+        <v>9.127196</v>
       </c>
       <c r="E3">
-        <v>43.2400016784668</v>
+        <v>32.35707473754883</v>
       </c>
       <c r="F3">
-        <v>23.72999954223633</v>
+        <v>29.3700008392334</v>
       </c>
       <c r="G3">
-        <v>-19.51000213623047</v>
+        <v>-2.98707389831543</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bezeq The Israel Telecommunication Corp Ltd</t>
+          <t>Elisa Corp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BZQIY</t>
+          <t>ELMUY</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.4091428571428571</v>
+        <v>1.0164943</v>
       </c>
       <c r="D4">
-        <v>2.864</v>
+        <v>10.164943</v>
       </c>
       <c r="E4">
-        <v>9.510000228881836</v>
+        <v>18.5</v>
       </c>
       <c r="F4">
-        <v>13.85000038146973</v>
+        <v>32.75</v>
       </c>
       <c r="G4">
-        <v>4.340000152587891</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chunghwa Telecom Co Ltd</t>
+          <t>Nexstar Media Group Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="C5">
-        <v>1.5573</v>
+        <v>3.210909090909091</v>
       </c>
       <c r="D5">
-        <v>15.573</v>
+        <v>35.32</v>
       </c>
       <c r="E5">
-        <v>31.54999923706055</v>
+        <v>63.29999923706055</v>
       </c>
       <c r="F5">
-        <v>43.15000152587891</v>
+        <v>210.1999969482422</v>
       </c>
       <c r="G5">
-        <v>11.60000228881836</v>
+        <v>146.8999977111816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Comcast Corp</t>
+          <t>Omnicom Group Inc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C6">
-        <v>0.8297450909090909</v>
+        <v>2.4</v>
       </c>
       <c r="D6">
-        <v>9.127196</v>
+        <v>26.4</v>
       </c>
       <c r="E6">
-        <v>32.35707473754883</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="F6">
-        <v>29.3700008392334</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="G6">
-        <v>-2.98707389831543</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CAR Group Limited</t>
+          <t>Orange SA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CSXXY</t>
+          <t>ORANY</t>
         </is>
       </c>
       <c r="C7">
-        <v>0.6796363636363636</v>
+        <v>0.7399</v>
       </c>
       <c r="D7">
-        <v>7.476</v>
+        <v>7.399</v>
       </c>
       <c r="E7">
-        <v>15.80000019073486</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="F7">
-        <v>36.77999877929688</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="G7">
-        <v>20.97999858856201</v>
+        <v>5.310000419616699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deutsche Telekom AG</t>
+          <t>PLDT Inc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DTEGY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8">
-        <v>0.7890909090909091</v>
+        <v>1.372727272727273</v>
       </c>
       <c r="D8">
-        <v>8.68</v>
+        <v>15.1</v>
       </c>
       <c r="E8">
-        <v>17.10000038146973</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="F8">
-        <v>32.34000015258789</v>
+        <v>20.94000053405762</v>
       </c>
       <c r="G8">
-        <v>15.23999977111816</v>
+        <v>-6.60999870300293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Elisa Corp</t>
+          <t>Publicis Groupe SA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ELMUY</t>
+          <t>PUBGY</t>
         </is>
       </c>
       <c r="C9">
-        <v>1.0164943</v>
+        <v>0.6485</v>
       </c>
       <c r="D9">
-        <v>10.164943</v>
+        <v>6.485</v>
       </c>
       <c r="E9">
-        <v>18.5</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="F9">
-        <v>32.75</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="G9">
-        <v>14.25</v>
+        <v>5.659999847412109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Informa Plc</t>
+          <t>Swisscom AG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IFJPY</t>
+          <t>SCMWY</t>
         </is>
       </c>
       <c r="C10">
-        <v>0.61175</v>
+        <v>2.4541</v>
       </c>
       <c r="D10">
-        <v>4.894</v>
+        <v>24.541</v>
       </c>
       <c r="E10">
-        <v>16.79999923706055</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="F10">
-        <v>22.36000061035156</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="G10">
-        <v>5.560001373291016</v>
+        <v>38.59000015258789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KDDI Corp</t>
+          <t>Sirius XM Holdings Inc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KDDIY</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="C11">
-        <v>0.2455</v>
+        <v>0.8618181818181818</v>
       </c>
       <c r="D11">
-        <v>0.491</v>
+        <v>9.48</v>
       </c>
       <c r="E11">
-        <v>12.64999961853027</v>
+        <v>44.5</v>
       </c>
       <c r="F11">
-        <v>16.35000038146973</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="G11">
-        <v>3.700000762939453</v>
+        <v>-16.44000053405762</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KT Corporation</t>
+          <t>SK Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="C12">
-        <v>0.6457499999999999</v>
+        <v>4.299850666666666</v>
       </c>
       <c r="D12">
-        <v>2.583</v>
+        <v>25.799104</v>
       </c>
       <c r="E12">
-        <v>14.09000015258789</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="F12">
-        <v>21.84000015258789</v>
+        <v>38.81999969482422</v>
       </c>
       <c r="G12">
-        <v>7.75</v>
+        <v>4.388370513916016</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Match Group Inc</t>
+          <t>Telenor ASA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>TELNY</t>
         </is>
       </c>
       <c r="C13">
-        <v>1.05</v>
+        <v>1.0068</v>
       </c>
       <c r="D13">
-        <v>3.15</v>
+        <v>10.068</v>
       </c>
       <c r="E13">
-        <v>17.10000038146973</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="F13">
-        <v>36.52999877929688</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G13">
-        <v>19.42999839782715</v>
+        <v>2.530000686645508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NetEase Inc</t>
+          <t>Millicom International Cellular SA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>TIGO</t>
         </is>
       </c>
       <c r="C14">
-        <v>1.377272727272727</v>
+        <v>3.296666666666667</v>
       </c>
       <c r="D14">
-        <v>15.15</v>
-      </c>
-      <c r="E14">
-        <v>43.06800079345703</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="F14">
-        <v>113.2699966430664</v>
-      </c>
-      <c r="G14">
-        <v>70.20199584960938</v>
+        <v>83.15000152587891</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NTT Inc</t>
+          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTTYY</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="C15">
-        <v>0.439</v>
+        <v>1.09075</v>
       </c>
       <c r="D15">
-        <v>0.878</v>
+        <v>10.9075</v>
       </c>
       <c r="E15">
-        <v>21.03499984741211</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="F15">
-        <v>23.73999977111816</v>
+        <v>17.68000030517578</v>
       </c>
       <c r="G15">
-        <v>2.704999923706055</v>
+        <v>-11.47999954223633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nexstar Media Group Inc.</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C16">
-        <v>3.210909090909091</v>
+        <v>2.295727272727273</v>
       </c>
       <c r="D16">
-        <v>35.32</v>
+        <v>25.253</v>
       </c>
       <c r="E16">
-        <v>63.29999923706055</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="F16">
-        <v>210.1999969482422</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="G16">
-        <v>146.8999977111816</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Omnicom Group Inc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>OMC</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>2.4</v>
-      </c>
-      <c r="D17">
-        <v>26.4</v>
-      </c>
-      <c r="E17">
-        <v>85.11000061035156</v>
-      </c>
-      <c r="F17">
-        <v>78.11000061035156</v>
-      </c>
-      <c r="G17">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Orange SA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ORANY</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>0.7399</v>
-      </c>
-      <c r="D18">
-        <v>7.399</v>
-      </c>
-      <c r="E18">
-        <v>15.14000034332275</v>
-      </c>
-      <c r="F18">
-        <v>20.45000076293945</v>
-      </c>
-      <c r="G18">
-        <v>5.310000419616699</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PLDT Inc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>1.372727272727273</v>
-      </c>
-      <c r="D19">
-        <v>15.1</v>
-      </c>
-      <c r="E19">
-        <v>27.54999923706055</v>
-      </c>
-      <c r="F19">
-        <v>20.94000053405762</v>
-      </c>
-      <c r="G19">
-        <v>-6.60999870300293</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Publicis Groupe SA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PUBGY</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>0.6485</v>
-      </c>
-      <c r="D20">
-        <v>6.485</v>
-      </c>
-      <c r="E20">
-        <v>17.20000076293945</v>
-      </c>
-      <c r="F20">
-        <v>22.86000061035156</v>
-      </c>
-      <c r="G20">
-        <v>5.659999847412109</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Rogers Communications Inc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>RCI</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>1.326</v>
-      </c>
-      <c r="D21">
-        <v>14.586</v>
-      </c>
-      <c r="E21">
-        <v>38.58000183105469</v>
-      </c>
-      <c r="F21">
-        <v>37.47999954223633</v>
-      </c>
-      <c r="G21">
-        <v>-1.100002288818359</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Swisscom AG</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SCMWY</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>2.4541</v>
-      </c>
-      <c r="D22">
-        <v>24.541</v>
-      </c>
-      <c r="E22">
-        <v>44.7400016784668</v>
-      </c>
-      <c r="F22">
-        <v>83.33000183105469</v>
-      </c>
-      <c r="G22">
-        <v>38.59000015258789</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Singapore Telecommunications Ltd</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SGAPY</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>1.0242</v>
-      </c>
-      <c r="D23">
-        <v>10.242</v>
-      </c>
-      <c r="E23">
-        <v>24.94000053405762</v>
-      </c>
-      <c r="F23">
-        <v>37.47999954223633</v>
-      </c>
-      <c r="G23">
-        <v>12.53999900817871</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sirius XM Holdings Inc</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>0.8618181818181818</v>
-      </c>
-      <c r="D24">
-        <v>9.48</v>
-      </c>
-      <c r="E24">
-        <v>44.5</v>
-      </c>
-      <c r="F24">
-        <v>28.05999946594238</v>
-      </c>
-      <c r="G24">
-        <v>-16.44000053405762</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SK Telecom Co Ltd</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SKM</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>4.299850666666666</v>
-      </c>
-      <c r="D25">
-        <v>25.799104</v>
-      </c>
-      <c r="E25">
-        <v>34.4316291809082</v>
-      </c>
-      <c r="F25">
-        <v>38.81999969482422</v>
-      </c>
-      <c r="G25">
-        <v>4.388370513916016</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AT&amp;T Inc</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>1.487818181818182</v>
-      </c>
-      <c r="D26">
-        <v>16.366</v>
-      </c>
-      <c r="E26">
-        <v>32.12235641479492</v>
-      </c>
-      <c r="F26">
-        <v>25.97999954223633</v>
-      </c>
-      <c r="G26">
-        <v>-6.142356872558594</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Telenor ASA</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>TELNY</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>1.0068</v>
-      </c>
-      <c r="D27">
-        <v>10.068</v>
-      </c>
-      <c r="E27">
-        <v>14.92000007629395</v>
-      </c>
-      <c r="F27">
-        <v>17.45000076293945</v>
-      </c>
-      <c r="G27">
-        <v>2.530000686645508</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Millicom International Cellular SA</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TIGO</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>3.296666666666667</v>
-      </c>
-      <c r="D28">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="F28">
-        <v>83.15000152587891</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Telstra Group Limited</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>TLGPY</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>0.6161818181818182</v>
-      </c>
-      <c r="D29">
-        <v>6.778</v>
-      </c>
-      <c r="E29">
-        <v>18.26000022888184</v>
-      </c>
-      <c r="F29">
-        <v>19.14999961853027</v>
-      </c>
-      <c r="G29">
-        <v>0.8899993896484375</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TLK</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>1.09075</v>
-      </c>
-      <c r="D30">
-        <v>10.9075</v>
-      </c>
-      <c r="E30">
-        <v>29.15999984741211</v>
-      </c>
-      <c r="F30">
-        <v>17.68000030517578</v>
-      </c>
-      <c r="G30">
-        <v>-11.47999954223633</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Telefonica Brasil SA</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VIV</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>0.6134545454545455</v>
-      </c>
-      <c r="D31">
-        <v>6.748</v>
-      </c>
-      <c r="E31">
-        <v>13.38000011444092</v>
-      </c>
-      <c r="F31">
-        <v>15.86999988555908</v>
-      </c>
-      <c r="G31">
-        <v>2.489999771118164</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Vodafone Group Public Limited Company</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>VOD</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>1.1265</v>
-      </c>
-      <c r="D32">
-        <v>11.265</v>
-      </c>
-      <c r="E32">
-        <v>24.43000030517578</v>
-      </c>
-      <c r="F32">
-        <v>15.3100004196167</v>
-      </c>
-      <c r="G32">
-        <v>-9.119999885559082</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Verizon Communications Inc</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>2.295727272727273</v>
-      </c>
-      <c r="D33">
-        <v>25.253</v>
-      </c>
-      <c r="E33">
-        <v>53.38000106811523</v>
-      </c>
-      <c r="F33">
-        <v>45.97999954223633</v>
-      </c>
-      <c r="G33">
         <v>-7.400001525878906</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Warner Music Group Corp</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>WMG</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>0.5271428571428571</v>
-      </c>
-      <c r="D34">
-        <v>3.69</v>
-      </c>
-      <c r="F34">
-        <v>29.30999946594238</v>
       </c>
     </row>
   </sheetData>

--- a/ProductionBuild/media.result.xlsx
+++ b/ProductionBuild/media.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,427 +367,1233 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturnover10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>shares500</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>totalspend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyearequityproj</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyeardivproj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>totalfiveyearview</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BCE Inc.</t>
+          <t>Nexstar Media Group Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BCE</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>2.161181818181818</v>
+          <t>NXST</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D2">
-        <v>23.773</v>
+        <v>3.210909090909091</v>
       </c>
       <c r="E2">
-        <v>43.2400016784668</v>
+        <v>35.32</v>
       </c>
       <c r="F2">
-        <v>23.72999954223633</v>
+        <v>63.29999923706055</v>
       </c>
       <c r="G2">
-        <v>-19.51000213623047</v>
+        <v>204.8200073242188</v>
+      </c>
+      <c r="H2">
+        <v>141.5200080871582</v>
+      </c>
+      <c r="I2">
+        <v>176.8400080871582</v>
+      </c>
+      <c r="J2">
+        <v>17.68400080871582</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>614.4600219726563</v>
+      </c>
+      <c r="M2">
+        <v>88.4200040435791</v>
+      </c>
+      <c r="N2">
+        <v>16.05454545454545</v>
+      </c>
+      <c r="O2">
+        <v>104.4745494981246</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Comcast Corp</t>
+          <t>NetEase Inc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CMCSA</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.8297450909090909</v>
+          <t>NTES</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D3">
-        <v>9.127196</v>
+        <v>1.377272727272727</v>
       </c>
       <c r="E3">
-        <v>32.35707473754883</v>
+        <v>15.15</v>
       </c>
       <c r="F3">
-        <v>29.3700008392334</v>
+        <v>43.06800079345703</v>
       </c>
       <c r="G3">
-        <v>-2.98707389831543</v>
+        <v>109.5400009155273</v>
+      </c>
+      <c r="H3">
+        <v>66.47200012207031</v>
+      </c>
+      <c r="I3">
+        <v>81.62200012207032</v>
+      </c>
+      <c r="J3">
+        <v>8.162200012207032</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>547.7000045776367</v>
+      </c>
+      <c r="M3">
+        <v>40.81100006103516</v>
+      </c>
+      <c r="N3">
+        <v>6.886363636363636</v>
+      </c>
+      <c r="O3">
+        <v>47.69736369739879</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elisa Corp</t>
+          <t>Swisscom AG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ELMUY</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>1.0164943</v>
+          <t>SCMWY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D4">
-        <v>10.164943</v>
+        <v>2.4541</v>
       </c>
       <c r="E4">
-        <v>18.5</v>
+        <v>24.541</v>
       </c>
       <c r="F4">
-        <v>32.75</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="G4">
-        <v>14.25</v>
+        <v>84.47000122070313</v>
+      </c>
+      <c r="H4">
+        <v>39.72999954223633</v>
+      </c>
+      <c r="I4">
+        <v>64.27099954223632</v>
+      </c>
+      <c r="J4">
+        <v>6.427099954223633</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <v>506.8200073242188</v>
+      </c>
+      <c r="M4">
+        <v>32.13549977111816</v>
+      </c>
+      <c r="N4">
+        <v>12.2705</v>
+      </c>
+      <c r="O4">
+        <v>44.40599977111816</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nexstar Media Group Inc.</t>
+          <t>SK Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NXST</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>3.210909090909091</v>
+          <t>SKM</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D5">
-        <v>35.32</v>
+        <v>4.299850666666666</v>
       </c>
       <c r="E5">
-        <v>63.29999923706055</v>
+        <v>25.799104</v>
       </c>
       <c r="F5">
-        <v>210.1999969482422</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="G5">
-        <v>146.8999977111816</v>
+        <v>37.95999908447266</v>
+      </c>
+      <c r="H5">
+        <v>3.528369903564453</v>
+      </c>
+      <c r="I5">
+        <v>29.32747390356445</v>
+      </c>
+      <c r="J5">
+        <v>2.932747390356445</v>
+      </c>
+      <c r="K5">
+        <v>14</v>
+      </c>
+      <c r="L5">
+        <v>531.4399871826172</v>
+      </c>
+      <c r="M5">
+        <v>14.66373695178222</v>
+      </c>
+      <c r="N5">
+        <v>21.49925333333333</v>
+      </c>
+      <c r="O5">
+        <v>36.16299028511555</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Omnicom Group Inc</t>
+          <t>CAR Group Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OMC</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>2.4</v>
+          <t>CSXXY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D6">
-        <v>26.4</v>
+        <v>0.6796363636363636</v>
       </c>
       <c r="E6">
-        <v>85.11000061035156</v>
+        <v>7.476</v>
       </c>
       <c r="F6">
-        <v>78.11000061035156</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="G6">
-        <v>-7</v>
+        <v>36.77999877929688</v>
+      </c>
+      <c r="H6">
+        <v>20.97999858856201</v>
+      </c>
+      <c r="I6">
+        <v>28.45599858856201</v>
+      </c>
+      <c r="J6">
+        <v>2.845599858856201</v>
+      </c>
+      <c r="K6">
+        <v>14</v>
+      </c>
+      <c r="L6">
+        <v>514.9199829101563</v>
+      </c>
+      <c r="M6">
+        <v>14.22799929428101</v>
+      </c>
+      <c r="N6">
+        <v>3.398181818181818</v>
+      </c>
+      <c r="O6">
+        <v>17.62618111246282</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Orange SA</t>
+          <t>Chunghwa Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORANY</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.7399</v>
+          <t>CHT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D7">
-        <v>7.399</v>
+        <v>1.5573</v>
       </c>
       <c r="E7">
-        <v>15.14000034332275</v>
+        <v>15.573</v>
       </c>
       <c r="F7">
-        <v>20.45000076293945</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="G7">
-        <v>5.310000419616699</v>
+        <v>43.18000030517578</v>
+      </c>
+      <c r="H7">
+        <v>11.63000106811523</v>
+      </c>
+      <c r="I7">
+        <v>27.20300106811523</v>
+      </c>
+      <c r="J7">
+        <v>2.720300106811524</v>
+      </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
+      <c r="L7">
+        <v>518.1600036621094</v>
+      </c>
+      <c r="M7">
+        <v>13.60150053405762</v>
+      </c>
+      <c r="N7">
+        <v>7.786499999999999</v>
+      </c>
+      <c r="O7">
+        <v>21.38800053405762</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLDT Inc</t>
+          <t>Elisa Corp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>1.372727272727273</v>
+          <t>ELMUY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D8">
-        <v>15.1</v>
+        <v>1.0164943</v>
       </c>
       <c r="E8">
-        <v>27.54999923706055</v>
+        <v>10.164943</v>
       </c>
       <c r="F8">
-        <v>20.94000053405762</v>
+        <v>18.5</v>
       </c>
       <c r="G8">
-        <v>-6.60999870300293</v>
+        <v>32.75</v>
+      </c>
+      <c r="H8">
+        <v>14.25</v>
+      </c>
+      <c r="I8">
+        <v>24.414943</v>
+      </c>
+      <c r="J8">
+        <v>2.4414943</v>
+      </c>
+      <c r="K8">
+        <v>16</v>
+      </c>
+      <c r="L8">
+        <v>524</v>
+      </c>
+      <c r="M8">
+        <v>12.2074715</v>
+      </c>
+      <c r="N8">
+        <v>5.0824715</v>
+      </c>
+      <c r="O8">
+        <v>17.289943</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Publicis Groupe SA</t>
+          <t>Deutsche Telekom AG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PUBGY</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.6485</v>
+          <t>DTEGY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D9">
-        <v>6.485</v>
+        <v>0.7890909090909091</v>
       </c>
       <c r="E9">
-        <v>17.20000076293945</v>
+        <v>8.68</v>
       </c>
       <c r="F9">
-        <v>22.86000061035156</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="G9">
-        <v>5.659999847412109</v>
+        <v>31.98999977111816</v>
+      </c>
+      <c r="H9">
+        <v>14.88999938964844</v>
+      </c>
+      <c r="I9">
+        <v>23.56999938964844</v>
+      </c>
+      <c r="J9">
+        <v>2.356999938964844</v>
+      </c>
+      <c r="K9">
+        <v>16</v>
+      </c>
+      <c r="L9">
+        <v>511.8399963378906</v>
+      </c>
+      <c r="M9">
+        <v>11.78499969482422</v>
+      </c>
+      <c r="N9">
+        <v>3.945454545454545</v>
+      </c>
+      <c r="O9">
+        <v>15.73045424027876</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swisscom AG</t>
+          <t>Singapore Telecommunications Ltd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SCMWY</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>2.4541</v>
+          <t>SGAPY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D10">
-        <v>24.541</v>
+        <v>1.0242</v>
       </c>
       <c r="E10">
-        <v>44.7400016784668</v>
+        <v>10.242</v>
       </c>
       <c r="F10">
-        <v>83.33000183105469</v>
+        <v>24.94000053405762</v>
       </c>
       <c r="G10">
-        <v>38.59000015258789</v>
+        <v>36.7400016784668</v>
+      </c>
+      <c r="H10">
+        <v>11.80000114440918</v>
+      </c>
+      <c r="I10">
+        <v>22.04200114440918</v>
+      </c>
+      <c r="J10">
+        <v>2.204200114440918</v>
+      </c>
+      <c r="K10">
+        <v>14</v>
+      </c>
+      <c r="L10">
+        <v>514.3600234985352</v>
+      </c>
+      <c r="M10">
+        <v>11.02100057220459</v>
+      </c>
+      <c r="N10">
+        <v>5.121</v>
+      </c>
+      <c r="O10">
+        <v>16.14200057220459</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sirius XM Holdings Inc</t>
+          <t>Match Group Inc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SIRI</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>0.8618181818181818</v>
+          <t>MTCH</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D11">
-        <v>9.48</v>
+        <v>1.05</v>
       </c>
       <c r="E11">
-        <v>44.5</v>
+        <v>3.15</v>
       </c>
       <c r="F11">
-        <v>28.05999946594238</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="G11">
-        <v>-16.44000053405762</v>
+        <v>35.65999984741211</v>
+      </c>
+      <c r="H11">
+        <v>18.55999946594238</v>
+      </c>
+      <c r="I11">
+        <v>21.70999946594238</v>
+      </c>
+      <c r="J11">
+        <v>2.170999946594238</v>
+      </c>
+      <c r="K11">
+        <v>15</v>
+      </c>
+      <c r="L11">
+        <v>534.8999977111816</v>
+      </c>
+      <c r="M11">
+        <v>10.85499973297119</v>
+      </c>
+      <c r="N11">
+        <v>5.25</v>
+      </c>
+      <c r="O11">
+        <v>16.10499973297119</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK Telecom Co Ltd</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SKM</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>4.299850666666666</v>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D12">
-        <v>25.799104</v>
+        <v>2.295727272727273</v>
       </c>
       <c r="E12">
-        <v>34.4316291809082</v>
+        <v>25.253</v>
       </c>
       <c r="F12">
-        <v>38.81999969482422</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="G12">
-        <v>4.388370513916016</v>
+        <v>47.22000122070313</v>
+      </c>
+      <c r="H12">
+        <v>-6.159999847412109</v>
+      </c>
+      <c r="I12">
+        <v>19.09300015258789</v>
+      </c>
+      <c r="J12">
+        <v>1.909300015258789</v>
+      </c>
+      <c r="K12">
+        <v>11</v>
+      </c>
+      <c r="L12">
+        <v>519.4200134277344</v>
+      </c>
+      <c r="M12">
+        <v>9.546500076293945</v>
+      </c>
+      <c r="N12">
+        <v>11.47863636363636</v>
+      </c>
+      <c r="O12">
+        <v>21.02513643993031</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Telenor ASA</t>
+          <t>Omnicom Group Inc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TELNY</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>1.0068</v>
+          <t>OMC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D13">
-        <v>10.068</v>
+        <v>2.4</v>
       </c>
       <c r="E13">
-        <v>14.92000007629395</v>
+        <v>26.4</v>
       </c>
       <c r="F13">
-        <v>17.45000076293945</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="G13">
-        <v>2.530000686645508</v>
+        <v>76.81999969482422</v>
+      </c>
+      <c r="H13">
+        <v>-8.290000915527344</v>
+      </c>
+      <c r="I13">
+        <v>18.10999908447265</v>
+      </c>
+      <c r="J13">
+        <v>1.810999908447265</v>
+      </c>
+      <c r="K13">
+        <v>7</v>
+      </c>
+      <c r="L13">
+        <v>537.7399978637695</v>
+      </c>
+      <c r="M13">
+        <v>9.054999542236327</v>
+      </c>
+      <c r="N13">
+        <v>12</v>
+      </c>
+      <c r="O13">
+        <v>21.05499954223633</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Millicom International Cellular SA</t>
+          <t>America Movil SAB de CV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TIGO</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>3.296666666666667</v>
+          <t>AMX</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D14">
-        <v>9.890000000000001</v>
+        <v>0.4173</v>
+      </c>
+      <c r="E14">
+        <v>4.173</v>
       </c>
       <c r="F14">
-        <v>83.15000152587891</v>
+        <v>12.56999969482422</v>
+      </c>
+      <c r="G14">
+        <v>26.04000091552734</v>
+      </c>
+      <c r="H14">
+        <v>13.47000122070313</v>
+      </c>
+      <c r="I14">
+        <v>17.64300122070313</v>
+      </c>
+      <c r="J14">
+        <v>1.764300122070313</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>520.8000183105469</v>
+      </c>
+      <c r="M14">
+        <v>8.821500610351563</v>
+      </c>
+      <c r="N14">
+        <v>2.0865</v>
+      </c>
+      <c r="O14">
+        <v>10.90800061035156</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
+          <t>Rogers Communications Inc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TLK</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>1.09075</v>
+          <t>RCI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D15">
-        <v>10.9075</v>
+        <v>1.326</v>
       </c>
       <c r="E15">
-        <v>29.15999984741211</v>
+        <v>14.586</v>
       </c>
       <c r="F15">
-        <v>17.68000030517578</v>
+        <v>38.58000183105469</v>
       </c>
       <c r="G15">
-        <v>-11.47999954223633</v>
+        <v>37.34999847412109</v>
+      </c>
+      <c r="H15">
+        <v>-1.230003356933594</v>
+      </c>
+      <c r="I15">
+        <v>13.35599664306641</v>
+      </c>
+      <c r="J15">
+        <v>1.335599664306641</v>
+      </c>
+      <c r="K15">
+        <v>14</v>
+      </c>
+      <c r="L15">
+        <v>522.8999786376953</v>
+      </c>
+      <c r="M15">
+        <v>6.677998321533202</v>
+      </c>
+      <c r="N15">
+        <v>6.630000000000001</v>
+      </c>
+      <c r="O15">
+        <v>13.3079983215332</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Orange SA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VZ</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>2.295727272727273</v>
+          <t>ORANY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
       </c>
       <c r="D16">
-        <v>25.253</v>
+        <v>0.7399</v>
       </c>
       <c r="E16">
-        <v>53.38000106811523</v>
+        <v>7.399</v>
       </c>
       <c r="F16">
-        <v>45.97999954223633</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="G16">
-        <v>-7.400001525878906</v>
+        <v>21</v>
+      </c>
+      <c r="H16">
+        <v>5.859999656677246</v>
+      </c>
+      <c r="I16">
+        <v>13.25899965667725</v>
+      </c>
+      <c r="J16">
+        <v>1.325899965667725</v>
+      </c>
+      <c r="K16">
+        <v>24</v>
+      </c>
+      <c r="L16">
+        <v>504</v>
+      </c>
+      <c r="M16">
+        <v>6.629499828338624</v>
+      </c>
+      <c r="N16">
+        <v>3.6995</v>
+      </c>
+      <c r="O16">
+        <v>10.32899982833862</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Telenor ASA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TELNY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>1.0068</v>
+      </c>
+      <c r="E17">
+        <v>10.068</v>
+      </c>
+      <c r="F17">
+        <v>14.92000007629395</v>
+      </c>
+      <c r="G17">
+        <v>17.45000076293945</v>
+      </c>
+      <c r="H17">
+        <v>2.530000686645508</v>
+      </c>
+      <c r="I17">
+        <v>12.59800068664551</v>
+      </c>
+      <c r="J17">
+        <v>1.259800068664551</v>
+      </c>
+      <c r="K17">
+        <v>29</v>
+      </c>
+      <c r="L17">
+        <v>506.0500221252441</v>
+      </c>
+      <c r="M17">
+        <v>6.299000343322754</v>
+      </c>
+      <c r="N17">
+        <v>5.034000000000001</v>
+      </c>
+      <c r="O17">
+        <v>11.33300034332276</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Publicis Groupe SA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUBGY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.6485</v>
+      </c>
+      <c r="E18">
+        <v>6.485</v>
+      </c>
+      <c r="F18">
+        <v>17.20000076293945</v>
+      </c>
+      <c r="G18">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="H18">
+        <v>5.309999465942383</v>
+      </c>
+      <c r="I18">
+        <v>11.79499946594238</v>
+      </c>
+      <c r="J18">
+        <v>1.179499946594238</v>
+      </c>
+      <c r="K18">
+        <v>23</v>
+      </c>
+      <c r="L18">
+        <v>517.7300052642822</v>
+      </c>
+      <c r="M18">
+        <v>5.897499732971191</v>
+      </c>
+      <c r="N18">
+        <v>3.2425</v>
+      </c>
+      <c r="O18">
+        <v>9.139999732971191</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AT&amp;T Inc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>1.487818181818182</v>
+      </c>
+      <c r="E19">
+        <v>16.366</v>
+      </c>
+      <c r="F19">
+        <v>32.12235641479492</v>
+      </c>
+      <c r="G19">
+        <v>26.61000061035156</v>
+      </c>
+      <c r="H19">
+        <v>-5.512355804443359</v>
+      </c>
+      <c r="I19">
+        <v>10.85364419555664</v>
+      </c>
+      <c r="J19">
+        <v>1.085364419555664</v>
+      </c>
+      <c r="K19">
+        <v>19</v>
+      </c>
+      <c r="L19">
+        <v>505.5900115966797</v>
+      </c>
+      <c r="M19">
+        <v>5.42682209777832</v>
+      </c>
+      <c r="N19">
+        <v>7.439090909090909</v>
+      </c>
+      <c r="O19">
+        <v>12.86591300686923</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KT Corporation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.6457499999999999</v>
+      </c>
+      <c r="E20">
+        <v>2.583</v>
+      </c>
+      <c r="F20">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="G20">
+        <v>21.69000053405762</v>
+      </c>
+      <c r="H20">
+        <v>7.600000381469727</v>
+      </c>
+      <c r="I20">
+        <v>10.18300038146973</v>
+      </c>
+      <c r="J20">
+        <v>1.018300038146973</v>
+      </c>
+      <c r="K20">
+        <v>24</v>
+      </c>
+      <c r="L20">
+        <v>520.5600128173828</v>
+      </c>
+      <c r="M20">
+        <v>5.091500190734863</v>
+      </c>
+      <c r="N20">
+        <v>3.22875</v>
+      </c>
+      <c r="O20">
+        <v>8.320250190734864</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Informa Plc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IFJPY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.61175</v>
+      </c>
+      <c r="E21">
+        <v>4.894</v>
+      </c>
+      <c r="F21">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="G21">
+        <v>21.72999954223633</v>
+      </c>
+      <c r="H21">
+        <v>4.930000305175781</v>
+      </c>
+      <c r="I21">
+        <v>9.824000305175781</v>
+      </c>
+      <c r="J21">
+        <v>0.9824000305175782</v>
+      </c>
+      <c r="K21">
+        <v>24</v>
+      </c>
+      <c r="L21">
+        <v>521.5199890136719</v>
+      </c>
+      <c r="M21">
+        <v>4.912000152587891</v>
+      </c>
+      <c r="N21">
+        <v>3.05875</v>
+      </c>
+      <c r="O21">
+        <v>7.970750152587891</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
   </sheetData>
